--- a/data/filtered/china_erotic.xlsx
+++ b/data/filtered/china_erotic.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I247"/>
+  <dimension ref="A1:N247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>2007-11-01</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1828115/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>2004-09-10</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1309029/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>1996-11-28</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1296463/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>1984-06-01</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1401129/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>1993-04-17</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302698/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>2007-05-17</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2043126/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>1972-11-16</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302036/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>2003-03-22</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1325005/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>1994-05-20</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10567361/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>2005-03-18</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308988/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>2011-09-01</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4883425/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>1996-06-14</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299072/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>1972-07-09</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307770/</t>
         </is>
@@ -1031,7 +1251,22 @@
           <t>1991-11-30</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/14016168/</t>
         </is>
@@ -1072,7 +1307,22 @@
           <t>1973-04-05</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303611/</t>
         </is>
@@ -1113,7 +1363,22 @@
           <t>1995-03-17</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298052/</t>
         </is>
@@ -1154,7 +1419,22 @@
           <t>1996-05-09</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1449776/</t>
         </is>
@@ -1195,7 +1475,22 @@
           <t>2002-11-07</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304337/</t>
         </is>
@@ -1236,7 +1531,22 @@
           <t>1980-11-26</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1982058/</t>
         </is>
@@ -1277,7 +1587,22 @@
           <t>1977-01-01</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2356794/</t>
         </is>
@@ -1318,7 +1643,22 @@
           <t>1993-01-29</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4236014/</t>
         </is>
@@ -1359,7 +1699,22 @@
           <t>1993-05-27</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4859384/</t>
         </is>
@@ -1400,7 +1755,22 @@
           <t>1982-05-06</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298960/</t>
         </is>
@@ -1441,7 +1811,22 @@
           <t>2013-07-25</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20515071/</t>
         </is>
@@ -1482,7 +1867,22 @@
           <t>1983-12-29</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300545/</t>
         </is>
@@ -1523,7 +1923,22 @@
           <t>1978-08-25</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4157980/</t>
         </is>
@@ -1564,7 +1979,22 @@
           <t>1993-09-08</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1401223/</t>
         </is>
@@ -1605,7 +2035,22 @@
           <t>1994-05-19</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3699947/</t>
         </is>
@@ -1646,7 +2091,22 @@
           <t>1992-12-03</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4819552/</t>
         </is>
@@ -1687,7 +2147,22 @@
           <t>1974-02-05</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1770510/</t>
         </is>
@@ -1728,7 +2203,22 @@
           <t>1993-10-28</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3783965/</t>
         </is>
@@ -1769,7 +2259,22 @@
           <t>1993-06-12</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305060/</t>
         </is>
@@ -1810,7 +2315,22 @@
           <t>1995-09-14</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3779111/</t>
         </is>
@@ -1851,7 +2371,22 @@
           <t>1997-03-13</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11639245/</t>
         </is>
@@ -1892,7 +2427,22 @@
           <t>1992-03-05</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4227664/</t>
         </is>
@@ -1933,7 +2483,22 @@
           <t>1994-01-27</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3920055/</t>
         </is>
@@ -1974,7 +2539,22 @@
           <t>1990-05-19</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11584182/</t>
         </is>
@@ -2015,7 +2595,22 @@
           <t>1974-01-17</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3801357/</t>
         </is>
@@ -2056,7 +2651,22 @@
           <t>1973-11-08</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1483705/</t>
         </is>
@@ -2097,7 +2707,22 @@
           <t>1991-12-06</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3757150/</t>
         </is>
@@ -2138,7 +2763,22 @@
           <t>1991-05-31</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5120686/</t>
         </is>
@@ -2179,7 +2819,22 @@
           <t>1973-02-01</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2138133/</t>
         </is>
@@ -2220,7 +2875,22 @@
           <t>1993-03-18</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298469/</t>
         </is>
@@ -2261,7 +2931,22 @@
           <t>1975-11-14</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3790589/</t>
         </is>
@@ -2302,7 +2987,22 @@
           <t>1991-05-09</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4227486/</t>
         </is>
@@ -2343,7 +3043,22 @@
           <t>1994-06-24</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3987608/</t>
         </is>
@@ -2384,7 +3099,22 @@
           <t>1996-06-07</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4859386/</t>
         </is>
@@ -2425,7 +3155,22 @@
           <t>1998-04-23</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11639538/</t>
         </is>
@@ -2466,7 +3211,22 @@
           <t>1995-05-25</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3765673/</t>
         </is>
@@ -2507,7 +3267,22 @@
           <t>1987-10-15</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20381366/</t>
         </is>
@@ -2548,7 +3323,22 @@
           <t>1991-05-10</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1301163/</t>
         </is>
@@ -2589,7 +3379,22 @@
           <t>2010-04-05</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4925924/</t>
         </is>
@@ -2630,7 +3435,22 @@
           <t>1994-04-08</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303204/</t>
         </is>
@@ -2671,7 +3491,22 @@
           <t>1996-03-21</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4808545/</t>
         </is>
@@ -2712,7 +3547,22 @@
           <t>1995-04-20</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3735839/</t>
         </is>
@@ -2753,7 +3603,22 @@
           <t>1979-02-08</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3998551/</t>
         </is>
@@ -2794,7 +3659,22 @@
           <t>2008-09-18</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4091908/</t>
         </is>
@@ -2835,7 +3715,22 @@
           <t>1976</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4819535/</t>
         </is>
@@ -2876,7 +3771,22 @@
           <t>1998-06-20</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3771089/</t>
         </is>
@@ -2917,7 +3827,22 @@
           <t>2009-03-05</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3837495/</t>
         </is>
@@ -2958,7 +3883,22 @@
           <t>1991-08-01</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3706530/</t>
         </is>
@@ -2999,7 +3939,22 @@
           <t>1996-08-10</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20379444/</t>
         </is>
@@ -3040,7 +3995,22 @@
           <t>2007-09-04</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2156064/</t>
         </is>
@@ -3081,7 +4051,22 @@
           <t>1993-04-17</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302557/</t>
         </is>
@@ -3122,7 +4107,22 @@
           <t>1992-03-12</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1850721/</t>
         </is>
@@ -3163,7 +4163,22 @@
           <t>2002-03-16</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3750513/</t>
         </is>
@@ -3204,7 +4219,22 @@
           <t>1994-10-13</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3743168/</t>
         </is>
@@ -3245,7 +4275,22 @@
           <t>2008-06-25</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3066671/</t>
         </is>
@@ -3286,7 +4331,22 @@
           <t>1992-11-19</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3559446/</t>
         </is>
@@ -3327,7 +4387,22 @@
           <t>1993-04-22</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1437840/</t>
         </is>
@@ -3368,7 +4443,22 @@
           <t>1997-10-09</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11758097/</t>
         </is>
@@ -3409,7 +4499,22 @@
           <t>2010-04-16</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4059243/</t>
         </is>
@@ -3450,7 +4555,22 @@
           <t>2018-10-26</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0</v>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30334399/</t>
         </is>
@@ -3491,7 +4611,22 @@
           <t>1999-03-01</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306786/</t>
         </is>
@@ -3532,7 +4667,22 @@
           <t>1998-03-26</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308190/</t>
         </is>
@@ -3573,7 +4723,22 @@
           <t>1975-01-09</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305969/</t>
         </is>
@@ -3614,7 +4779,22 @@
           <t>1993-11-04</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1301112/</t>
         </is>
@@ -3655,7 +4835,22 @@
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6383557/</t>
         </is>
@@ -3696,7 +4891,22 @@
           <t>2000-09-23</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3742949/</t>
         </is>
@@ -3737,7 +4947,22 @@
           <t>1992-10-15</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/23060058/</t>
         </is>
@@ -3778,7 +5003,22 @@
           <t>1991-05-23</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3871526/</t>
         </is>
@@ -3819,7 +5059,22 @@
           <t>1995-05-06</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304735/</t>
         </is>
@@ -3860,7 +5115,22 @@
           <t>1998-12-05</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3713675/</t>
         </is>
@@ -3901,7 +5171,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1903037/</t>
         </is>
@@ -3942,7 +5227,22 @@
           <t>1976-06-26</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3794184/</t>
         </is>
@@ -3983,7 +5283,22 @@
           <t>1990-10-12</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4328069/</t>
         </is>
@@ -4024,7 +5339,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3434539/</t>
         </is>
@@ -4065,7 +5395,22 @@
           <t>2003-12-07</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5395234/</t>
         </is>
@@ -4106,7 +5451,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3818017/</t>
         </is>
@@ -4147,7 +5507,22 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34813513/</t>
         </is>
@@ -4188,7 +5563,22 @@
           <t>2011-04-14</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6114876/</t>
         </is>
@@ -4229,7 +5619,22 @@
           <t>1990-11-10</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19897562/</t>
         </is>
@@ -4270,7 +5675,22 @@
           <t>1984-05-23</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1479825/</t>
         </is>
@@ -4311,7 +5731,22 @@
           <t>2004-10-28</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1316694/</t>
         </is>
@@ -4352,7 +5787,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26760448/</t>
         </is>
@@ -4393,7 +5843,22 @@
           <t>1992-04-03</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6968158/</t>
         </is>
@@ -4434,7 +5899,22 @@
           <t>1998-07-04</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1929753/</t>
         </is>
@@ -4475,7 +5955,22 @@
           <t>1996-06-06</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2973634/</t>
         </is>
@@ -4516,7 +6011,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1818543/</t>
         </is>
@@ -4557,7 +6067,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4858343/</t>
         </is>
@@ -4598,7 +6123,22 @@
           <t>1992-03-13</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/14009755/</t>
         </is>
@@ -4639,7 +6179,22 @@
           <t>1992-05-20</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2039585/</t>
         </is>
@@ -4680,7 +6235,22 @@
           <t>2015-09-15</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25981796/</t>
         </is>
@@ -4721,7 +6291,22 @@
           <t>1998-09-18</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3755289/</t>
         </is>
@@ -4762,7 +6347,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4319847/</t>
         </is>
@@ -4803,7 +6403,22 @@
           <t>1994-03-17</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2159087/</t>
         </is>
@@ -4844,7 +6459,22 @@
           <t>1973-12-21</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3797862/</t>
         </is>
@@ -4885,7 +6515,22 @@
           <t>1994-09-09</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3932719/</t>
         </is>
@@ -4926,7 +6571,22 @@
           <t>1986-06-28</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5179821/</t>
         </is>
@@ -4967,7 +6627,22 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26709655/</t>
         </is>
@@ -5008,7 +6683,22 @@
           <t>1991-01-23</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4224317/</t>
         </is>
@@ -5049,7 +6739,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304486/</t>
         </is>
@@ -5090,7 +6795,22 @@
           <t>1983-08-12</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>1</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2354893/</t>
         </is>
@@ -5131,7 +6851,22 @@
           <t>1999-12-23</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305438/</t>
         </is>
@@ -5172,7 +6907,22 @@
           <t>1977-09-30</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3791443/</t>
         </is>
@@ -5213,7 +6963,22 @@
           <t>1995-04-20</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4016502/</t>
         </is>
@@ -5254,7 +7019,22 @@
           <t>1993-05-06</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2155691/</t>
         </is>
@@ -5295,7 +7075,22 @@
           <t>1992-10-15</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305176/</t>
         </is>
@@ -5336,7 +7131,22 @@
           <t>2015-01-29</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26279166/</t>
         </is>
@@ -5377,7 +7187,22 @@
           <t>1998-06-12</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11639348/</t>
         </is>
@@ -5418,7 +7243,22 @@
           <t>2011-05-01</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4275580/</t>
         </is>
@@ -5459,7 +7299,22 @@
           <t>2018-12-13</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26752558/</t>
         </is>
@@ -5500,7 +7355,22 @@
           <t>1997-10-24</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3763243/</t>
         </is>
@@ -5541,7 +7411,22 @@
           <t>1993-10-28</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1307275/</t>
         </is>
@@ -5582,7 +7467,22 @@
           <t>1985-09-26</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2355276/</t>
         </is>
@@ -5623,7 +7523,22 @@
           <t>1992-01-09</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20366175/</t>
         </is>
@@ -5664,7 +7579,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26794164/</t>
         </is>
@@ -5705,7 +7635,22 @@
           <t>1990-09-24</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3136387/</t>
         </is>
@@ -5746,7 +7691,22 @@
           <t>2012-08-29</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10744833/</t>
         </is>
@@ -5787,7 +7747,22 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26322729/</t>
         </is>
@@ -5828,7 +7803,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2298000/</t>
         </is>
@@ -5869,7 +7859,22 @@
           <t>2001-04-26</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11627126/</t>
         </is>
@@ -5910,7 +7915,22 @@
           <t>1995-03-23</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1755344/</t>
         </is>
@@ -5951,7 +7971,22 @@
           <t>1984</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25886465/</t>
         </is>
@@ -5992,7 +8027,22 @@
           <t>1993-05-26</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2332539/</t>
         </is>
@@ -6033,7 +8083,22 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26322732/</t>
         </is>
@@ -6074,7 +8139,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25986164/</t>
         </is>
@@ -6115,7 +8195,22 @@
           <t>1991-04-29</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5366664/</t>
         </is>
@@ -6156,7 +8251,22 @@
           <t>1999-05-13</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20495848/</t>
         </is>
@@ -6197,7 +8307,22 @@
           <t>1983-10-28</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303749/</t>
         </is>
@@ -6238,7 +8363,22 @@
           <t>1982</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26754903/</t>
         </is>
@@ -6279,7 +8419,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0</v>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4862570/</t>
         </is>
@@ -6320,7 +8475,22 @@
           <t>1995</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26801015/</t>
         </is>
@@ -6361,7 +8531,22 @@
           <t>2014-03-25</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24858573/</t>
         </is>
@@ -6402,7 +8587,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26581190/</t>
         </is>
@@ -6443,7 +8643,22 @@
           <t>1992-05-28</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2081071/</t>
         </is>
@@ -6484,7 +8699,22 @@
           <t>1991-12-12</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25707503/</t>
         </is>
@@ -6525,7 +8755,22 @@
           <t>1987-08-09</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>1</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26730480/</t>
         </is>
@@ -6566,7 +8811,22 @@
           <t>1977-11-18</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3999736/</t>
         </is>
@@ -6607,7 +8867,22 @@
           <t>1992-08-05</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25743034/</t>
         </is>
@@ -6648,7 +8923,22 @@
           <t>1993-10-14</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26734630/</t>
         </is>
@@ -6689,7 +8979,22 @@
           <t>1992-10-29</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20389760/</t>
         </is>
@@ -6730,7 +9035,22 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26795024/</t>
         </is>
@@ -6771,7 +9091,22 @@
           <t>1989-04-22</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26744081/</t>
         </is>
@@ -6812,7 +9147,22 @@
           <t>1973-11-29</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3809036/</t>
         </is>
@@ -6853,7 +9203,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2210230/</t>
         </is>
@@ -6894,7 +9259,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26796637/</t>
         </is>
@@ -6935,7 +9315,22 @@
           <t>2016-01-14</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26614645/</t>
         </is>
@@ -6976,7 +9371,22 @@
           <t>1980-04-04</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2028865/</t>
         </is>
@@ -7017,7 +9427,22 @@
           <t>1999-12-09</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11636425/</t>
         </is>
@@ -7058,7 +9483,22 @@
           <t>1995-02-10</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26341082/</t>
         </is>
@@ -7099,7 +9539,22 @@
           <t>1992-12-18</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19941733/</t>
         </is>
@@ -7140,7 +9595,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4116943/</t>
         </is>
@@ -7181,7 +9651,22 @@
           <t>1993-06-24</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305687/</t>
         </is>
@@ -7222,7 +9707,22 @@
           <t>2024-11-01</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/37105408/</t>
         </is>
@@ -7263,7 +9763,22 @@
           <t>1993-05-13</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2325871/</t>
         </is>
@@ -7304,7 +9819,22 @@
           <t>1988-12-15</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2339415/</t>
         </is>
@@ -7345,7 +9875,22 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>0</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26729557/</t>
         </is>
@@ -7386,7 +9931,22 @@
           <t>1992-12-10</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3571767/</t>
         </is>
@@ -7427,7 +9987,22 @@
           <t>2000-01-21</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25806707/</t>
         </is>
@@ -7468,7 +10043,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1979035/</t>
         </is>
@@ -7509,7 +10099,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26732252/</t>
         </is>
@@ -7550,7 +10155,22 @@
           <t>1987-08-16</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0</v>
+      </c>
+      <c r="N174" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26734641/</t>
         </is>
@@ -7591,7 +10211,22 @@
           <t>2014-06-19</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/22734960/</t>
         </is>
@@ -7632,7 +10267,22 @@
           <t>1996-01-16</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11593163/</t>
         </is>
@@ -7673,7 +10323,22 @@
           <t>2011-10-06</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>1</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6796160/</t>
         </is>
@@ -7714,7 +10379,22 @@
           <t>1993-09-16</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4891792/</t>
         </is>
@@ -7755,7 +10435,22 @@
           <t>2014-01-02</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/22556008/</t>
         </is>
@@ -7796,7 +10491,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26219711/</t>
         </is>
@@ -7837,7 +10547,22 @@
           <t>1994-03-10</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3122954/</t>
         </is>
@@ -7878,7 +10603,22 @@
           <t>2002-10-01</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20280201/</t>
         </is>
@@ -7919,7 +10659,22 @@
           <t>1990-11-15</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20378787/</t>
         </is>
@@ -7960,7 +10715,22 @@
           <t>1996-08-30</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>1</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19961095/</t>
         </is>
@@ -8001,7 +10771,22 @@
           <t>2013-11-12</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0</v>
+      </c>
+      <c r="N185" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24294773/</t>
         </is>
@@ -8042,7 +10827,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3555371/</t>
         </is>
@@ -8083,7 +10883,22 @@
           <t>1999</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5145738/</t>
         </is>
@@ -8124,7 +10939,22 @@
           <t>1993-07-23</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304103/</t>
         </is>
@@ -8165,7 +10995,22 @@
           <t>2015-04-16</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0</v>
+      </c>
+      <c r="N189" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25853739/</t>
         </is>
@@ -8206,7 +11051,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25889728/</t>
         </is>
@@ -8247,7 +11107,22 @@
           <t>2012-03-29</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5989846/</t>
         </is>
@@ -8288,7 +11163,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26730043/</t>
         </is>
@@ -8329,7 +11219,22 @@
           <t>1993-08-30</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>1</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20379434/</t>
         </is>
@@ -8370,7 +11275,22 @@
           <t>1995-04-06</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25964083/</t>
         </is>
@@ -8411,7 +11331,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>0</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1295960/</t>
         </is>
@@ -8452,7 +11387,22 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11610648/</t>
         </is>
@@ -8493,7 +11443,22 @@
           <t>1993-03-26</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298568/</t>
         </is>
@@ -8534,7 +11499,22 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11639545/</t>
         </is>
@@ -8575,7 +11555,22 @@
           <t>1988-01-14</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6866797/</t>
         </is>
@@ -8616,7 +11611,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26829793/</t>
         </is>
@@ -8657,7 +11667,22 @@
           <t>1994</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I201" t="n">
+        <v>0</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2370800/</t>
         </is>
@@ -8698,7 +11723,22 @@
           <t>2002</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20495849/</t>
         </is>
@@ -8735,7 +11775,22 @@
           <t>2005</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26732197/</t>
         </is>
@@ -8776,7 +11831,22 @@
           <t>1993-08-19</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>1</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6038543/</t>
         </is>
@@ -8817,7 +11887,22 @@
           <t>1993-02-19</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3317333/</t>
         </is>
@@ -8858,7 +11943,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3093298/</t>
         </is>
@@ -8899,7 +11999,22 @@
           <t>1993-09-29</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3780230/</t>
         </is>
@@ -8940,7 +12055,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26593716/</t>
         </is>
@@ -8981,7 +12111,22 @@
           <t>2018-07-28</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>1</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26951654/</t>
         </is>
@@ -9022,7 +12167,22 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25798285/</t>
         </is>
@@ -9063,7 +12223,22 @@
           <t>1993</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3190510/</t>
         </is>
@@ -9104,7 +12279,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19897610/</t>
         </is>
@@ -9145,7 +12335,22 @@
           <t>2000-05-05</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
+      <c r="I213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L213" t="n">
+        <v>0</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0</v>
+      </c>
+      <c r="N213" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24736570/</t>
         </is>
@@ -9182,7 +12387,22 @@
           <t>1995-11-02</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr">
+      <c r="I214" t="n">
+        <v>0</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L214" t="n">
+        <v>0</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26733922/</t>
         </is>
@@ -9223,7 +12443,22 @@
           <t>1995-12-09</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>0</v>
+      </c>
+      <c r="M215" t="n">
+        <v>1</v>
+      </c>
+      <c r="N215" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299333/</t>
         </is>
@@ -9264,7 +12499,22 @@
           <t>1999-11-27</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
+      <c r="I216" t="n">
+        <v>0</v>
+      </c>
+      <c r="J216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L216" t="n">
+        <v>0</v>
+      </c>
+      <c r="M216" t="n">
+        <v>1</v>
+      </c>
+      <c r="N216" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2297134/</t>
         </is>
@@ -9305,7 +12555,22 @@
           <t>2017-09-15</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0</v>
+      </c>
+      <c r="N217" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27016589/</t>
         </is>
@@ -9346,7 +12611,22 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="I218" t="n">
+        <v>0</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L218" t="n">
+        <v>0</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3338905/</t>
         </is>
@@ -9387,7 +12667,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr">
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L219" t="n">
+        <v>0</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0</v>
+      </c>
+      <c r="N219" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1949604/</t>
         </is>
@@ -9428,7 +12723,22 @@
           <t>1998</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr">
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L220" t="n">
+        <v>0</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2256080/</t>
         </is>
@@ -9469,7 +12779,22 @@
           <t>1998-10-31</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr">
+      <c r="I221" t="n">
+        <v>0</v>
+      </c>
+      <c r="J221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L221" t="n">
+        <v>0</v>
+      </c>
+      <c r="M221" t="n">
+        <v>1</v>
+      </c>
+      <c r="N221" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24752791/</t>
         </is>
@@ -9510,7 +12835,22 @@
           <t>2004-03-24</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr">
+      <c r="I222" t="n">
+        <v>0</v>
+      </c>
+      <c r="J222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3339411/</t>
         </is>
@@ -9551,7 +12891,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I223" t="n">
+        <v>0</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L223" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20284984/</t>
         </is>
@@ -9592,7 +12947,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr">
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0</v>
+      </c>
+      <c r="N224" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25761135/</t>
         </is>
@@ -9633,7 +13003,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr">
+      <c r="I225" t="n">
+        <v>0</v>
+      </c>
+      <c r="J225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L225" t="n">
+        <v>0</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25788667/</t>
         </is>
@@ -9674,7 +13059,22 @@
           <t>2015-04-24</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
+      <c r="I226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L226" t="n">
+        <v>0</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25917896/</t>
         </is>
@@ -9715,7 +13115,22 @@
           <t>2013-12-17</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr">
+      <c r="I227" t="n">
+        <v>0</v>
+      </c>
+      <c r="J227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L227" t="n">
+        <v>0</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25769969/</t>
         </is>
@@ -9756,7 +13171,22 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
+      <c r="I228" t="n">
+        <v>0</v>
+      </c>
+      <c r="J228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L228" t="n">
+        <v>0</v>
+      </c>
+      <c r="M228" t="n">
+        <v>0</v>
+      </c>
+      <c r="N228" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/19973807/</t>
         </is>
@@ -9797,7 +13227,22 @@
           <t>1998-06-12</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
+      <c r="I229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L229" t="n">
+        <v>0</v>
+      </c>
+      <c r="M229" t="n">
+        <v>0</v>
+      </c>
+      <c r="N229" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2364066/</t>
         </is>
@@ -9838,7 +13283,22 @@
           <t>2000-08-13</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
+      <c r="I230" t="n">
+        <v>0</v>
+      </c>
+      <c r="J230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L230" t="n">
+        <v>1</v>
+      </c>
+      <c r="M230" t="n">
+        <v>0</v>
+      </c>
+      <c r="N230" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24748831/</t>
         </is>
@@ -9879,7 +13339,22 @@
           <t>2010-10-12</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
+      <c r="I231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L231" t="n">
+        <v>0</v>
+      </c>
+      <c r="M231" t="n">
+        <v>0</v>
+      </c>
+      <c r="N231" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5267375/</t>
         </is>
@@ -9920,7 +13395,22 @@
           <t>2003-09-12</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="I232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="n">
+        <v>0</v>
+      </c>
+      <c r="N232" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25961815/</t>
         </is>
@@ -9961,7 +13451,22 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
+      <c r="I233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
+      <c r="M233" t="n">
+        <v>0</v>
+      </c>
+      <c r="N233" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25825432/</t>
         </is>
@@ -10002,7 +13507,22 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
+      <c r="I234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L234" t="n">
+        <v>0</v>
+      </c>
+      <c r="M234" t="n">
+        <v>0</v>
+      </c>
+      <c r="N234" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25825433/</t>
         </is>
@@ -10043,7 +13563,22 @@
           <t>2005-08-03</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
+      <c r="I235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L235" t="n">
+        <v>1</v>
+      </c>
+      <c r="M235" t="n">
+        <v>0</v>
+      </c>
+      <c r="N235" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3431116/</t>
         </is>
@@ -10084,7 +13619,22 @@
           <t>1996</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
+      <c r="I236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L236" t="n">
+        <v>0</v>
+      </c>
+      <c r="M236" t="n">
+        <v>0</v>
+      </c>
+      <c r="N236" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25824518/</t>
         </is>
@@ -10125,7 +13675,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
+      <c r="I237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L237" t="n">
+        <v>0</v>
+      </c>
+      <c r="M237" t="n">
+        <v>0</v>
+      </c>
+      <c r="N237" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3141459/</t>
         </is>
@@ -10166,7 +13731,22 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
+      <c r="I238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L238" t="n">
+        <v>0</v>
+      </c>
+      <c r="M238" t="n">
+        <v>0</v>
+      </c>
+      <c r="N238" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25814963/</t>
         </is>
@@ -10207,7 +13787,22 @@
           <t>2013-11-11</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
+      <c r="I239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L239" t="n">
+        <v>0</v>
+      </c>
+      <c r="M239" t="n">
+        <v>0</v>
+      </c>
+      <c r="N239" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25768127/</t>
         </is>
@@ -10248,7 +13843,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
+      <c r="I240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L240" t="n">
+        <v>0</v>
+      </c>
+      <c r="M240" t="n">
+        <v>0</v>
+      </c>
+      <c r="N240" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25702949/</t>
         </is>
@@ -10289,7 +13899,22 @@
           <t>2013-12-18</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
+      <c r="I241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L241" t="n">
+        <v>0</v>
+      </c>
+      <c r="M241" t="n">
+        <v>0</v>
+      </c>
+      <c r="N241" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25795316/</t>
         </is>
@@ -10330,7 +13955,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr">
+      <c r="I242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L242" t="n">
+        <v>0</v>
+      </c>
+      <c r="M242" t="n">
+        <v>0</v>
+      </c>
+      <c r="N242" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25748605/</t>
         </is>
@@ -10371,7 +14011,22 @@
           <t>2013</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr">
+      <c r="I243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L243" t="n">
+        <v>0</v>
+      </c>
+      <c r="M243" t="n">
+        <v>0</v>
+      </c>
+      <c r="N243" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25801053/</t>
         </is>
@@ -10412,7 +14067,22 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr">
+      <c r="I244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L244" t="n">
+        <v>0</v>
+      </c>
+      <c r="M244" t="n">
+        <v>0</v>
+      </c>
+      <c r="N244" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26667331/</t>
         </is>
@@ -10453,7 +14123,22 @@
           <t>2012-02-10</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr">
+      <c r="I245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L245" t="n">
+        <v>0</v>
+      </c>
+      <c r="M245" t="n">
+        <v>0</v>
+      </c>
+      <c r="N245" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6110569/</t>
         </is>
@@ -10494,7 +14179,22 @@
           <t>2011-08-05</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
+      <c r="I246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L246" t="n">
+        <v>1</v>
+      </c>
+      <c r="M246" t="n">
+        <v>0</v>
+      </c>
+      <c r="N246" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6130488/</t>
         </is>
@@ -10535,7 +14235,22 @@
           <t>2013-10-12</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr">
+      <c r="I247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L247" t="n">
+        <v>0</v>
+      </c>
+      <c r="M247" t="n">
+        <v>1</v>
+      </c>
+      <c r="N247" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24878091/</t>
         </is>
